--- a/TrafagSalesExporter/docs/Issue_Log_Ingo_2026-08-12.xlsx
+++ b/TrafagSalesExporter/docs/Issue_Log_Ingo_2026-08-12.xlsx
@@ -204,19 +204,25 @@
     <x:t>Posting Date fehlt bei TR ES</x:t>
   </x:si>
   <x:si>
+    <x:t>Läuft</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ingo / Spanien</x:t>
   </x:si>
   <x:si>
-    <x:t>FacturasTB im Exportskript joinen und FechaAsiento als PostingDate ausgeben, danach im ES-Mapping auf SalesRecord.PostingDate mappen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>docs/FINANCE_ISSUE_LOG_ANDREAS_2026-07-28.md §1; docs/FINANCE_ES_BUCHUNGSDATUM_2026-08-03.md</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Join-Schlüssel zu den Lieferscheinpositionen offen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS KORRIGIERT: stand als "Warten auf andere". Sage HAT das Buchungsdatum, es heisst FacturasTB.FechaAsiento und ist in der Stichprobe zu 100 % gefüllt; es fehlt nur im Export, und der Export ist unser. Offen sind der Join-Schlüssel und die Behandlung von Gutschriften. Am 12.08.2026 gemessen: PostingDate fehlt bei 5'731 von 5'731 ES-Zeilen. WICHTIGE KORREKTUR gegenüber der Analyse vom 28.07.: die 250 ES-Zeilen ohne jedes Datum fallen NICHT aus der Auswertung, sie sind schlechter eingeordnet. Die Spalte Finance | Date nutzt die Fallback-Kette bis zum ExtractionDate, deshalb landen sie im Monat des Exportlaufs. Nachgerechnet: ES hat im August nach Belegdatum 86 Zeilen, im Export 336, Differenz genau 250; UK 91 gegenüber 107, Differenz genau 16. Der laufende Monat wird also um 266 Zeilen aufgebläht.</x:t>
+    <x:t>Paket auf den spanischen Sage-Server kopieren, Export einmal laufen lassen und dabei die Zeilenzahl gegen den Vorlauf prüfen, danach PostingDate beim Standort Spanien zuordnen und reimportieren</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SageSpainExportPackage/SageSpainFinalExportPackage/Export-SageSpainSalesCsv.ps1; Run-SpainRangeExportAndUpload-AllInOne.ps1; docs/FINANCE_ES_BUCHUNGSDATUM_2026-08-03.md Abschnitt 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RDP-Sitzung auf dem spanischen Sage-Server; Join-Schlüssel bis zur Messung eine Annahme</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAND 17.08.2026: das Feld ist im Exportskript EINGEBAUT und wartet nur noch auf den Lauf in Spanien. Die SQL selektiert FacturasTB.FechaAsiento als PostingDate und FacturasTB.Asiento als PostingDocument, per OUTER APPLY mit TOP 1 statt JOIN, weil 70 von 3'642 Rechnungsschlüsseln mehrere Buchungszeilen haben und ein JOIN die Verkaufszeilen vervielfacht hätte. Belegt ist bisher NUR die Syntax (ScriptDom, alle vier Varianten, mit Gegenprobe); Trefferquote, Schlüsselrichtigkeit und Gutschriften sind offen. Beim ersten Lauf zwingend die Zeilenzahl gegen den Vorlauf prüfen. Nebenbefund: die Paket-Zip war seit dem rclone-Fix veraltet und wurde neu gebaut. STATUS KORRIGIERT: stand als "Warten auf andere". Sage HAT das Buchungsdatum, es heisst FacturasTB.FechaAsiento und ist in der Stichprobe zu 100 % gefüllt; es fehlt nur im Export, und der Export ist unser. Offen sind der Join-Schlüssel und die Behandlung von Gutschriften. Am 12.08.2026 gemessen: PostingDate fehlt bei 5'731 von 5'731 ES-Zeilen. WICHTIGE KORREKTUR gegenüber der Analyse vom 28.07.: die 250 ES-Zeilen ohne jedes Datum fallen NICHT aus der Auswertung, sie sind schlechter eingeordnet. Die Spalte Finance | Date nutzt die Fallback-Kette bis zum ExtractionDate, deshalb landen sie im Monat des Exportlaufs. Nachgerechnet: ES hat im August nach Belegdatum 86 Zeilen, im Export 336, Differenz genau 250; UK 91 gegenüber 107, Differenz genau 16. Der laufende Monat wird also um 266 Zeilen aufgebläht.</x:t>
   </x:si>
   <x:si>
     <x:t>ISS-003</x:t>
@@ -1443,20 +1449,20 @@
       <x:c r="D7" s="9" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
-        <x:v>37</x:v>
+      <x:c r="E7" s="12" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F7" s="7" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G7" s="7" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H7" s="9" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I7" s="9" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
         <x:v>41</x:v>
@@ -1465,13 +1471,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L7" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M7" s="9" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="N7" s="9" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:14">
@@ -1479,28 +1485,28 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E8" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F8" s="6" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J8" s="2" t="s">
         <x:v>41</x:v>
@@ -1515,7 +1521,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N8" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:14">
@@ -1523,13 +1529,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="8" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C9" s="9" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D9" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
         <x:v>17</x:v>
@@ -1544,7 +1550,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="I9" s="9" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
         <x:v>41</x:v>
@@ -1559,7 +1565,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N9" s="9" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:14">
@@ -1567,13 +1573,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C10" s="9" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D10" s="9" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E10" s="10" t="s">
         <x:v>37</x:v>
@@ -1582,13 +1588,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="G10" s="7" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H10" s="9" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I10" s="9" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
         <x:v>24</x:v>
@@ -1603,7 +1609,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N10" s="9" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:14">
@@ -1611,13 +1617,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="8" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C11" s="9" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D11" s="9" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E11" s="10" t="s">
         <x:v>37</x:v>
@@ -1626,13 +1632,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="G11" s="7" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H11" s="9" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I11" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
         <x:v>41</x:v>
@@ -1644,10 +1650,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="M11" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N11" s="9" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:14">
@@ -1655,28 +1661,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="8" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E12" s="13" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F12" s="11" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G12" s="7" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H12" s="9" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I12" s="9" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J12" s="7" t="s">
         <x:v>32</x:v>
@@ -1688,10 +1694,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="M12" s="9" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="N12" s="9" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:14">
@@ -1699,28 +1705,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="8" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D13" s="9" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E13" s="13" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F13" s="7" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G13" s="7" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H13" s="9" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I13" s="9" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="J13" s="7" t="s">
         <x:v>24</x:v>
@@ -1732,10 +1738,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="M13" s="9" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="N13" s="9" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:14">
@@ -1743,13 +1749,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E14" s="10" t="s">
         <x:v>37</x:v>
@@ -1761,10 +1767,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H14" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I14" s="4" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="J14" s="2" t="s">
         <x:v>24</x:v>
@@ -1779,7 +1785,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N14" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:14">
@@ -1787,13 +1793,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E15" s="10" t="s">
         <x:v>37</x:v>
@@ -1802,16 +1808,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H15" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="I15" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="J15" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K15" s="2" t="s">
         <x:v>23</x:v>
@@ -1820,10 +1826,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="M15" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="N15" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:14">
@@ -1831,16 +1837,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E16" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
         <x:v>38</x:v>
@@ -1849,10 +1855,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H16" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I16" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J16" s="2" t="s">
         <x:v>22</x:v>
@@ -1867,7 +1873,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N16" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:14">
@@ -1875,13 +1881,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D17" s="9" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E17" s="10" t="s">
         <x:v>37</x:v>
@@ -1890,19 +1896,19 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="G17" s="7" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H17" s="9" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="I17" s="9" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J17" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K17" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="L17" s="7" t="s">
         <x:v>24</x:v>
@@ -1911,7 +1917,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N17" s="9" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:14">
@@ -1919,31 +1925,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E18" s="10" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H18" s="4" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="I18" s="4" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="J18" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K18" s="2" t="s">
         <x:v>23</x:v>
@@ -1952,10 +1958,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="M18" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="N18" s="4" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:14">
@@ -1963,13 +1969,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C19" s="4" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E19" s="10" t="s">
         <x:v>37</x:v>
@@ -1978,16 +1984,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H19" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="I19" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J19" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="K19" s="2" t="s">
         <x:v>23</x:v>
@@ -1996,10 +2002,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="M19" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="N19" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:14">
@@ -2007,13 +2013,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E20" s="10" t="s">
         <x:v>37</x:v>
@@ -2022,28 +2028,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H20" s="4" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="I20" s="4" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="J20" s="2" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K20" s="2" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L20" s="2" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="M20" s="4" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="N20" s="4" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2070,82 +2076,82 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="15" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B1" s="16" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2" ht="46" customHeight="1">
       <x:c r="A2" s="17" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B2" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2" ht="46" customHeight="1">
       <x:c r="A3" s="17" t="s">
-        <x:v>172</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B3" s="14" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2" ht="46" customHeight="1">
       <x:c r="A4" s="17" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B4" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2" ht="46" customHeight="1">
       <x:c r="A5" s="17" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B5" s="14" t="s">
-        <x:v>177</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2" ht="46" customHeight="1">
       <x:c r="A6" s="17" t="s">
-        <x:v>178</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B6" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2" ht="46" customHeight="1">
       <x:c r="A7" s="17" t="s">
-        <x:v>180</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B7" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2" ht="46" customHeight="1">
       <x:c r="A8" s="17" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B8" s="14" t="s">
-        <x:v>183</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2" ht="46" customHeight="1">
       <x:c r="A9" s="17" t="s">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B9" s="14" t="s">
-        <x:v>185</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2" ht="46" customHeight="1">
       <x:c r="A10" s="17" t="s">
-        <x:v>186</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B10" s="14" t="s">
-        <x:v>187</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
